--- a/data/extra_material/interview_questions.xlsx
+++ b/data/extra_material/interview_questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\Chatbot-Evaluation-Framework\data\extra_material\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\CEP-guide\data\extra_material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1C7BC0-B98C-46DC-9634-AB318D7950AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01420C41-920A-4E57-95BB-7929C943D94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>Question</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>What (additional) background information should the chatbot be able to "understand" so that its responses appear well-informed?</t>
-  </si>
-  <si>
-    <t>Areas for Future Development</t>
   </si>
   <si>
     <t>How would you feel if the chatbot flagged certain responses for risk reasons (e.g., ethical reasons, data protection)?</t>
@@ -451,7 +448,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -462,10 +459,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -473,7 +470,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -484,10 +481,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -495,7 +492,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -506,7 +503,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -517,7 +514,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
@@ -528,57 +525,57 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
